--- a/June_Invoice_Profit_Analysis_ExactFormat.xlsx
+++ b/June_Invoice_Profit_Analysis_ExactFormat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hy 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9741450B-0DC0-4917-B786-5D8614BF491E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52AF766-555F-4511-8C13-7B3005608208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -564,26 +564,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -635,10 +615,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -961,40 +961,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="14" t="s">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
       <c r="N2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1041,10 +1041,10 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1060,7 +1060,7 @@
         <f t="shared" ref="F4:F31" si="0">D4*E4</f>
         <v>800</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="31">
         <f>SUM(F4:F10)*1.2095</f>
         <v>10881.96826</v>
       </c>
@@ -1068,19 +1068,19 @@
       <c r="I4" s="5"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="6">
+      <c r="L4" s="31">
         <f>SUM(K4:K10)</f>
         <v>20570.866141732284</v>
       </c>
       <c r="M4" s="3"/>
-      <c r="N4" s="6">
+      <c r="N4" s="31">
         <f>L4-G4</f>
         <v>9688.8978817322841</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="34" t="s">
+      <c r="A5" s="29"/>
+      <c r="B5" s="24" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1096,18 +1096,18 @@
         <f t="shared" si="0"/>
         <v>450</v>
       </c>
-      <c r="G5" s="7"/>
+      <c r="G5" s="32"/>
       <c r="H5" s="3"/>
       <c r="I5" s="5"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="7"/>
+      <c r="L5" s="32"/>
       <c r="M5" s="3"/>
-      <c r="N5" s="7"/>
+      <c r="N5" s="32"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="29"/>
+      <c r="B6" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1123,18 +1123,18 @@
         <f t="shared" si="0"/>
         <v>450</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="3"/>
       <c r="I6" s="5"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="7"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="7"/>
+      <c r="N6" s="32"/>
     </row>
     <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="34" t="s">
+      <c r="A7" s="29"/>
+      <c r="B7" s="24" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1150,7 +1150,7 @@
         <f t="shared" si="0"/>
         <v>2079</v>
       </c>
-      <c r="G7" s="7"/>
+      <c r="G7" s="32"/>
       <c r="H7" s="3" t="s">
         <v>24</v>
       </c>
@@ -1165,13 +1165,13 @@
         <f>I7*J7</f>
         <v>20570.866141732284</v>
       </c>
-      <c r="L7" s="7"/>
+      <c r="L7" s="32"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="7"/>
+      <c r="N7" s="32"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="34" t="s">
+      <c r="A8" s="29"/>
+      <c r="B8" s="24" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -1187,18 +1187,18 @@
         <f t="shared" si="0"/>
         <v>675</v>
       </c>
-      <c r="G8" s="7"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="3"/>
       <c r="I8" s="5"/>
       <c r="J8" s="4"/>
       <c r="K8" s="5"/>
-      <c r="L8" s="7"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="7"/>
+      <c r="N8" s="32"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="34" t="s">
+      <c r="A9" s="29"/>
+      <c r="B9" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1214,18 +1214,18 @@
         <f t="shared" si="0"/>
         <v>4008.6</v>
       </c>
-      <c r="G9" s="7"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="3"/>
       <c r="I9" s="5"/>
       <c r="J9" s="4"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="7"/>
+      <c r="L9" s="32"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="7"/>
+      <c r="N9" s="32"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="30"/>
+      <c r="B10" s="24" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1241,20 +1241,20 @@
         <f t="shared" si="0"/>
         <v>534.48</v>
       </c>
-      <c r="G10" s="8"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="3"/>
       <c r="I10" s="5"/>
       <c r="J10" s="4"/>
       <c r="K10" s="5"/>
-      <c r="L10" s="8"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="3"/>
-      <c r="N10" s="8"/>
+      <c r="N10" s="33"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="24" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1270,7 +1270,7 @@
         <f t="shared" si="0"/>
         <v>425</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="31">
         <f>SUM(F11:F14)*1.2095</f>
         <v>2015.63175</v>
       </c>
@@ -1278,19 +1278,19 @@
       <c r="I11" s="5"/>
       <c r="J11" s="4"/>
       <c r="K11" s="5"/>
-      <c r="L11" s="6">
+      <c r="L11" s="31">
         <f>SUM(K11:K14)</f>
         <v>6233.5958005249349</v>
       </c>
       <c r="M11" s="3"/>
-      <c r="N11" s="6">
+      <c r="N11" s="31">
         <f>L11-G11</f>
         <v>4217.9640505249354</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="34" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1306,7 +1306,7 @@
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="G12" s="7"/>
+      <c r="G12" s="32"/>
       <c r="H12" s="3" t="s">
         <v>24</v>
       </c>
@@ -1321,13 +1321,13 @@
         <f>I12*J12</f>
         <v>6233.5958005249349</v>
       </c>
-      <c r="L12" s="7"/>
+      <c r="L12" s="32"/>
       <c r="M12" s="3"/>
-      <c r="N12" s="7"/>
+      <c r="N12" s="32"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="34" t="s">
+      <c r="A13" s="29"/>
+      <c r="B13" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1343,18 +1343,18 @@
         <f t="shared" si="0"/>
         <v>742.5</v>
       </c>
-      <c r="G13" s="7"/>
+      <c r="G13" s="32"/>
       <c r="H13" s="3"/>
       <c r="I13" s="5"/>
       <c r="J13" s="4"/>
       <c r="K13" s="5"/>
-      <c r="L13" s="7"/>
+      <c r="L13" s="32"/>
       <c r="M13" s="3"/>
-      <c r="N13" s="7"/>
+      <c r="N13" s="32"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="30"/>
+      <c r="B14" s="24" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1370,20 +1370,20 @@
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="G14" s="8"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="3"/>
       <c r="I14" s="5"/>
       <c r="J14" s="4"/>
       <c r="K14" s="5"/>
-      <c r="L14" s="8"/>
+      <c r="L14" s="33"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="8"/>
+      <c r="N14" s="33"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="24" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -1399,7 +1399,7 @@
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="31">
         <f>SUM(F15:F19)*1.2095</f>
         <v>6764.5823124999997</v>
       </c>
@@ -1407,19 +1407,19 @@
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
       <c r="K15" s="5"/>
-      <c r="L15" s="6">
+      <c r="L15" s="31">
         <f>SUM(K15:K19)</f>
         <v>6880</v>
       </c>
       <c r="M15" s="3"/>
-      <c r="N15" s="6">
+      <c r="N15" s="31">
         <f>L15-G15</f>
         <v>115.41768750000028</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="34" t="s">
+      <c r="A16" s="29"/>
+      <c r="B16" s="24" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1435,18 +1435,18 @@
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="G16" s="7"/>
+      <c r="G16" s="32"/>
       <c r="H16" s="3"/>
       <c r="I16" s="5"/>
       <c r="J16" s="4"/>
       <c r="K16" s="5"/>
-      <c r="L16" s="7"/>
+      <c r="L16" s="32"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="7"/>
+      <c r="N16" s="32"/>
     </row>
     <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="34" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="24" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1462,7 +1462,7 @@
         <f t="shared" si="0"/>
         <v>1068.75</v>
       </c>
-      <c r="G17" s="7"/>
+      <c r="G17" s="32"/>
       <c r="H17" s="3" t="s">
         <v>34</v>
       </c>
@@ -1476,13 +1476,13 @@
         <f>I17*J17</f>
         <v>6880</v>
       </c>
-      <c r="L17" s="7"/>
+      <c r="L17" s="32"/>
       <c r="M17" s="3"/>
-      <c r="N17" s="7"/>
+      <c r="N17" s="32"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="34" t="s">
+      <c r="A18" s="29"/>
+      <c r="B18" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -1498,18 +1498,18 @@
         <f t="shared" si="0"/>
         <v>2491.875</v>
       </c>
-      <c r="G18" s="7"/>
+      <c r="G18" s="32"/>
       <c r="H18" s="3"/>
       <c r="I18" s="5"/>
       <c r="J18" s="4"/>
       <c r="K18" s="5"/>
-      <c r="L18" s="7"/>
+      <c r="L18" s="32"/>
       <c r="M18" s="3"/>
-      <c r="N18" s="7"/>
+      <c r="N18" s="32"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="34" t="s">
+      <c r="A19" s="30"/>
+      <c r="B19" s="24" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1525,20 +1525,20 @@
         <f t="shared" si="0"/>
         <v>332.25</v>
       </c>
-      <c r="G19" s="8"/>
+      <c r="G19" s="33"/>
       <c r="H19" s="3"/>
       <c r="I19" s="5"/>
       <c r="J19" s="4"/>
       <c r="K19" s="5"/>
-      <c r="L19" s="8"/>
+      <c r="L19" s="33"/>
       <c r="M19" s="3"/>
-      <c r="N19" s="8"/>
+      <c r="N19" s="33"/>
     </row>
     <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="24" t="s">
         <v>33</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1554,7 +1554,7 @@
         <f t="shared" si="0"/>
         <v>1068.75</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="31">
         <f>SUM(F20:F25)*1.2095</f>
         <v>13529.164624999999</v>
       </c>
@@ -1571,19 +1571,19 @@
         <f>I20*J20</f>
         <v>6800</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="31">
         <f>SUM(K20:K25)</f>
         <v>13600</v>
       </c>
       <c r="M20" s="3"/>
-      <c r="N20" s="6">
+      <c r="N20" s="31">
         <f>L20-G20</f>
         <v>70.835375000000568</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="34" t="s">
+      <c r="A21" s="29"/>
+      <c r="B21" s="24" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -1599,7 +1599,7 @@
         <f t="shared" si="0"/>
         <v>1068.75</v>
       </c>
-      <c r="G21" s="7"/>
+      <c r="G21" s="32"/>
       <c r="H21" s="3" t="s">
         <v>34</v>
       </c>
@@ -1613,13 +1613,13 @@
         <f>I21*J21</f>
         <v>6800</v>
       </c>
-      <c r="L21" s="7"/>
+      <c r="L21" s="32"/>
       <c r="M21" s="3"/>
-      <c r="N21" s="7"/>
+      <c r="N21" s="32"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="34" t="s">
+      <c r="A22" s="29"/>
+      <c r="B22" s="24" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1635,18 +1635,18 @@
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="G22" s="7"/>
+      <c r="G22" s="32"/>
       <c r="H22" s="3"/>
       <c r="I22" s="5"/>
       <c r="J22" s="4"/>
       <c r="K22" s="5"/>
-      <c r="L22" s="7"/>
+      <c r="L22" s="32"/>
       <c r="M22" s="3"/>
-      <c r="N22" s="7"/>
+      <c r="N22" s="32"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="34" t="s">
+      <c r="A23" s="29"/>
+      <c r="B23" s="24" t="s">
         <v>32</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1662,18 +1662,18 @@
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="G23" s="7"/>
+      <c r="G23" s="32"/>
       <c r="H23" s="3"/>
       <c r="I23" s="5"/>
       <c r="J23" s="4"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="7"/>
+      <c r="L23" s="32"/>
       <c r="M23" s="3"/>
-      <c r="N23" s="7"/>
+      <c r="N23" s="32"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="34" t="s">
+      <c r="A24" s="29"/>
+      <c r="B24" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -1689,18 +1689,18 @@
         <f t="shared" si="0"/>
         <v>4983.75</v>
       </c>
-      <c r="G24" s="7"/>
+      <c r="G24" s="32"/>
       <c r="H24" s="3"/>
       <c r="I24" s="5"/>
       <c r="J24" s="4"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="7"/>
+      <c r="L24" s="32"/>
       <c r="M24" s="3"/>
-      <c r="N24" s="7"/>
+      <c r="N24" s="32"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="34" t="s">
+      <c r="A25" s="30"/>
+      <c r="B25" s="24" t="s">
         <v>27</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -1716,20 +1716,20 @@
         <f t="shared" si="0"/>
         <v>664.5</v>
       </c>
-      <c r="G25" s="8"/>
+      <c r="G25" s="33"/>
       <c r="H25" s="3"/>
       <c r="I25" s="5"/>
       <c r="J25" s="4"/>
       <c r="K25" s="5"/>
-      <c r="L25" s="8"/>
+      <c r="L25" s="33"/>
       <c r="M25" s="3"/>
-      <c r="N25" s="8"/>
+      <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="24" t="s">
         <v>37</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -1745,7 +1745,7 @@
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="31">
         <f>SUM(F26:F31)*1.2095</f>
         <v>8309.533508999999</v>
       </c>
@@ -1753,19 +1753,19 @@
       <c r="I26" s="5"/>
       <c r="J26" s="4"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="6">
+      <c r="L26" s="31">
         <f>SUM(K26:K31)</f>
         <v>8440.9448818897636</v>
       </c>
       <c r="M26" s="3"/>
-      <c r="N26" s="6">
+      <c r="N26" s="31">
         <f>L26-G26</f>
         <v>131.41137288976461</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="34" t="s">
+      <c r="A27" s="29"/>
+      <c r="B27" s="24" t="s">
         <v>38</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -1781,18 +1781,18 @@
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="G27" s="7"/>
+      <c r="G27" s="32"/>
       <c r="H27" s="3"/>
       <c r="I27" s="5"/>
       <c r="J27" s="4"/>
       <c r="K27" s="5"/>
-      <c r="L27" s="7"/>
+      <c r="L27" s="32"/>
       <c r="M27" s="3"/>
-      <c r="N27" s="7"/>
+      <c r="N27" s="32"/>
     </row>
     <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="34" t="s">
+      <c r="A28" s="29"/>
+      <c r="B28" s="24" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -1808,7 +1808,7 @@
         <f t="shared" si="0"/>
         <v>251.1</v>
       </c>
-      <c r="G28" s="7"/>
+      <c r="G28" s="32"/>
       <c r="H28" s="3" t="s">
         <v>40</v>
       </c>
@@ -1823,13 +1823,13 @@
         <f>I28*J28</f>
         <v>2440.9448818897636</v>
       </c>
-      <c r="L28" s="7"/>
+      <c r="L28" s="32"/>
       <c r="M28" s="3"/>
-      <c r="N28" s="7"/>
+      <c r="N28" s="32"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="34" t="s">
+      <c r="A29" s="29"/>
+      <c r="B29" s="24" t="s">
         <v>41</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -1845,20 +1845,20 @@
         <f t="shared" si="0"/>
         <v>1450</v>
       </c>
-      <c r="G29" s="7"/>
+      <c r="G29" s="32"/>
       <c r="H29" s="3"/>
       <c r="I29" s="5"/>
       <c r="J29" s="4"/>
       <c r="K29" s="5">
         <v>6000</v>
       </c>
-      <c r="L29" s="7"/>
+      <c r="L29" s="32"/>
       <c r="M29" s="3"/>
-      <c r="N29" s="7"/>
+      <c r="N29" s="32"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="34" t="s">
+      <c r="A30" s="29"/>
+      <c r="B30" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -1874,17 +1874,17 @@
         <f t="shared" si="0"/>
         <v>3060.99</v>
       </c>
-      <c r="G30" s="7"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="3"/>
       <c r="I30" s="5"/>
       <c r="J30" s="4"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="7"/>
+      <c r="L30" s="32"/>
       <c r="M30" s="3"/>
-      <c r="N30" s="7"/>
+      <c r="N30" s="32"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="12"/>
+      <c r="A31" s="30"/>
       <c r="B31" s="3" t="s">
         <v>27</v>
       </c>
@@ -1901,183 +1901,192 @@
         <f t="shared" si="0"/>
         <v>408.13200000000001</v>
       </c>
-      <c r="G31" s="8"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="3"/>
       <c r="I31" s="5"/>
       <c r="J31" s="4"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="8"/>
+      <c r="L31" s="33"/>
       <c r="M31" s="3"/>
-      <c r="N31" s="8"/>
+      <c r="N31" s="33"/>
     </row>
     <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
     </row>
     <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="19" t="str">
+      <c r="A36" s="9" t="str">
         <f>A4</f>
         <v>INV/2026/06/001</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="10">
         <f>G4</f>
         <v>10881.96826</v>
       </c>
-      <c r="C36" s="21">
+      <c r="C36" s="11">
         <f>L4</f>
         <v>20570.866141732284</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="12">
         <f>C36-B36</f>
         <v>9688.8978817322841</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="13">
         <f t="shared" ref="E36:E41" si="1">D36/C36</f>
         <v>0.47100096879617226</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="str">
+      <c r="A37" s="14" t="str">
         <f>A11</f>
         <v>INV/2026/06/002</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B37" s="15">
         <f>G11</f>
         <v>2015.63175</v>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="16">
         <f>L11</f>
         <v>6233.5958005249349</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="12">
         <f t="shared" ref="D37:D40" si="2">C37-B37</f>
         <v>4217.9640505249354</v>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="13">
         <f t="shared" si="1"/>
         <v>0.67665023294736848</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="19" t="str">
+      <c r="A38" s="9" t="str">
         <f>A15</f>
         <v>INV/2026/06/003</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="10">
         <f>G15</f>
         <v>6764.5823124999997</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="11">
         <f>L15</f>
         <v>6880</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="12">
         <f t="shared" si="2"/>
         <v>115.41768750000028</v>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="13">
         <f t="shared" si="1"/>
         <v>1.677582667151167E-2</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="str">
+      <c r="A39" s="14" t="str">
         <f>A20</f>
         <v>INV/2026/06/004</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="15">
         <f>G20</f>
         <v>13529.164624999999</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="16">
         <f>L20</f>
         <v>13600</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="12">
         <f t="shared" si="2"/>
         <v>70.835375000000568</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="13">
         <f t="shared" si="1"/>
         <v>5.2084834558823951E-3</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="19" t="str">
+      <c r="A40" s="9" t="str">
         <f>A26</f>
         <v>INV/2026/06/005</v>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="10">
         <f>G26</f>
         <v>8309.533508999999</v>
       </c>
-      <c r="C40" s="21">
+      <c r="C40" s="11">
         <f>L26</f>
         <v>8440.9448818897636</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="12">
         <f t="shared" si="2"/>
         <v>131.41137288976461</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="13">
         <f t="shared" si="1"/>
         <v>1.5568324959888158E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="28">
+      <c r="B41" s="18">
         <f>SUM(B36:B40)</f>
         <v>41500.880456500003</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="19">
         <f>SUM(C36:C40)</f>
         <v>55725.406824146979</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="20">
         <f>SUM(D36:D40)</f>
         <v>14224.526367646986</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="21">
         <f t="shared" si="1"/>
         <v>0.25526105915270236</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="33">
+      <c r="B42" s="23">
         <f>SUM(F9+F13+F18+F24+F30)</f>
         <v>15287.715</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H2"/>
+    <mergeCell ref="A26:A31"/>
+    <mergeCell ref="L20:L25"/>
+    <mergeCell ref="L26:L31"/>
+    <mergeCell ref="G20:G25"/>
+    <mergeCell ref="N11:N14"/>
+    <mergeCell ref="G11:G14"/>
+    <mergeCell ref="G15:G19"/>
+    <mergeCell ref="G26:G31"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A4:A10"/>
@@ -2094,15 +2103,6 @@
     <mergeCell ref="N20:N25"/>
     <mergeCell ref="L4:L10"/>
     <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A26:A31"/>
-    <mergeCell ref="L20:L25"/>
-    <mergeCell ref="L26:L31"/>
-    <mergeCell ref="G20:G25"/>
-    <mergeCell ref="N11:N14"/>
-    <mergeCell ref="G11:G14"/>
-    <mergeCell ref="G15:G19"/>
-    <mergeCell ref="G26:G31"/>
-    <mergeCell ref="H2"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0.25" header="0.5" footer="0.5"/>
